--- a/20261027/15_台账真值检验/input/三厂换刀记录.xlsx
+++ b/20261027/15_台账真值检验/input/三厂换刀记录.xlsx
@@ -8,20 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\abc\workBoddyHome刀具\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2899C8BA-BC84-400D-B805-79321C32F63B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DBC9A26-79C8-43B3-9FF3-9864729AC07F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="水性 4152" sheetId="2" r:id="rId1"/>
-    <sheet name="刀具调查" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="53">
   <si>
     <t>主副轴</t>
   </si>
@@ -53,9 +52,6 @@
     <t>备注</t>
   </si>
   <si>
-    <t>主轴</t>
-  </si>
-  <si>
     <t>是</t>
   </si>
   <si>
@@ -174,165 +170,6 @@
   </si>
   <si>
     <t>刀尖破损  刀寿100</t>
-  </si>
-  <si>
-    <t>T15</t>
-  </si>
-  <si>
-    <t>T1515</t>
-  </si>
-  <si>
-    <t>设备号</t>
-  </si>
-  <si>
-    <t>主/副轴</t>
-  </si>
-  <si>
-    <t>刀具名称</t>
-  </si>
-  <si>
-    <t>工序</t>
-  </si>
-  <si>
-    <t>每班加工件数</t>
-  </si>
-  <si>
-    <t>正常寿命件数</t>
-  </si>
-  <si>
-    <t>寿命是否稳定</t>
-  </si>
-  <si>
-    <t>换刀判断方式</t>
-  </si>
-  <si>
-    <t>历史崩刃频率</t>
-  </si>
-  <si>
-    <t>崩刃是否有火花</t>
-  </si>
-  <si>
-    <t>崩刃影响</t>
-  </si>
-  <si>
-    <t>工艺是否稳定</t>
-  </si>
-  <si>
-    <t>产品变化情况</t>
-  </si>
-  <si>
-    <t>是否容易记录换刀原因</t>
-  </si>
-  <si>
-    <t>推荐RUL</t>
-  </si>
-  <si>
-    <t>推荐崩刃</t>
-  </si>
-  <si>
-    <t>T8</t>
-  </si>
-  <si>
-    <t>T0808</t>
-  </si>
-  <si>
-    <t>钻头</t>
-  </si>
-  <si>
-    <t>螺纹底孔</t>
-  </si>
-  <si>
-    <t>否</t>
-  </si>
-  <si>
-    <t>刀具破损</t>
-  </si>
-  <si>
-    <t>次/日</t>
-  </si>
-  <si>
-    <t>尺寸不良</t>
-  </si>
-  <si>
-    <t>C5G25同缸径品番段取，刀具基本共通</t>
-  </si>
-  <si>
-    <t>切断刀片</t>
-  </si>
-  <si>
-    <t>切断</t>
-  </si>
-  <si>
-    <t>设备报警</t>
-  </si>
-  <si>
-    <t>T1300</t>
-  </si>
-  <si>
-    <t>六方底孔</t>
-  </si>
-  <si>
-    <t>次/周</t>
-  </si>
-  <si>
-    <t>单一品番生产</t>
-  </si>
-  <si>
-    <t>T1400</t>
-  </si>
-  <si>
-    <t>六方冲头</t>
-  </si>
-  <si>
-    <t>冲削刀头</t>
-  </si>
-  <si>
-    <t>沟槽刀</t>
-  </si>
-  <si>
-    <t>沟槽粗加工</t>
-  </si>
-  <si>
-    <t>加工机种较多，刀具不共通</t>
-  </si>
-  <si>
-    <t>T17</t>
-  </si>
-  <si>
-    <t>T1717</t>
-  </si>
-  <si>
-    <t>外径刀</t>
-  </si>
-  <si>
-    <t>主侧外径车削</t>
-  </si>
-  <si>
-    <t>稳定</t>
-  </si>
-  <si>
-    <t>到达刀具寿命，设备报警</t>
-  </si>
-  <si>
-    <t>此设备品番刀具通用</t>
-  </si>
-  <si>
-    <t>T31</t>
-  </si>
-  <si>
-    <t>T3131</t>
-  </si>
-  <si>
-    <t>副侧外径车削粗加工</t>
-  </si>
-  <si>
-    <t>T33</t>
-  </si>
-  <si>
-    <t>T3133</t>
-  </si>
-  <si>
-    <t>副侧外径车削精加工</t>
   </si>
   <si>
     <t>2026/10/26/9：20</t>
@@ -377,17 +214,12 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -426,7 +258,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -456,16 +288,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -764,13 +586,13 @@
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -782,25 +604,25 @@
         <v>46255.613888888904</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
         <v>15</v>
       </c>
-      <c r="H2" t="s">
-        <v>16</v>
-      </c>
       <c r="I2" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J2" s="4"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
       <c r="A3" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3" s="2">
         <v>2</v>
@@ -812,25 +634,25 @@
         <v>46258.116666666698</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J3" s="2"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D4" s="2">
         <v>3</v>
@@ -842,27 +664,27 @@
         <v>46259.429166666698</v>
       </c>
       <c r="G4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="I4" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="18" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D5" s="2">
         <v>4</v>
@@ -874,25 +696,25 @@
         <v>46260.569444444402</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J5" s="2"/>
     </row>
     <row r="6" spans="1:10" ht="18" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D6" s="2">
         <v>5</v>
@@ -904,25 +726,25 @@
         <v>46260.947916666701</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J6" s="2"/>
     </row>
     <row r="7" spans="1:10" ht="18" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D7" s="2">
         <v>6</v>
@@ -934,25 +756,25 @@
         <v>46261.434027777803</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J7" s="2"/>
     </row>
     <row r="8" spans="1:10" ht="18" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D8" s="2">
         <v>7</v>
@@ -964,25 +786,25 @@
         <v>46261.90625</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J8" s="2"/>
     </row>
     <row r="9" spans="1:10" ht="18" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D9" s="2">
         <v>8</v>
@@ -994,25 +816,25 @@
         <v>46262.427083333299</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J9" s="2"/>
     </row>
     <row r="10" spans="1:10" ht="18" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D10" s="2">
         <v>9</v>
@@ -1024,25 +846,25 @@
         <v>46262.746527777803</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J10" s="2"/>
     </row>
     <row r="11" spans="1:10" ht="18" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D11" s="2">
         <v>10</v>
@@ -1054,25 +876,25 @@
         <v>46265.618055555598</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J11" s="2"/>
     </row>
     <row r="12" spans="1:10" ht="18" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D12" s="2">
         <v>11</v>
@@ -1084,25 +906,25 @@
         <v>46266.443749999999</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J12" s="2"/>
     </row>
     <row r="13" spans="1:10" ht="18" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D13" s="2">
         <v>12</v>
@@ -1114,25 +936,25 @@
         <v>46266.969444444403</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J13" s="2"/>
     </row>
     <row r="14" spans="1:10" ht="18" customHeight="1">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -1144,24 +966,24 @@
         <v>46267.8034722222</v>
       </c>
       <c r="G14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="18" customHeight="1">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -1173,24 +995,24 @@
         <v>46268.586111111101</v>
       </c>
       <c r="G15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="18" customHeight="1">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1202,24 +1024,24 @@
         <v>46268.84375</v>
       </c>
       <c r="G16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="18" customHeight="1">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D17">
         <v>16</v>
@@ -1228,56 +1050,56 @@
         <v>46268.847916666702</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="18" customHeight="1">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D18">
         <v>17</v>
       </c>
       <c r="E18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F18" s="6">
         <v>46271.729166666701</v>
       </c>
       <c r="G18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="18" customHeight="1">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1289,24 +1111,24 @@
         <v>46272.666666666701</v>
       </c>
       <c r="G19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="18" customHeight="1">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1318,24 +1140,24 @@
         <v>46273.458333333299</v>
       </c>
       <c r="G20" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="18" customHeight="1">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C21" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1347,24 +1169,24 @@
         <v>46274.458333333299</v>
       </c>
       <c r="G21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="16.5">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1376,24 +1198,24 @@
         <v>46275.347222222197</v>
       </c>
       <c r="G22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="16.5">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C23" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1405,24 +1227,24 @@
         <v>46275.743055555598</v>
       </c>
       <c r="G23" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H23" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="16.5">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C24" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1434,24 +1256,24 @@
         <v>46276.998611111099</v>
       </c>
       <c r="G24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I24" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="16.5">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C25" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1463,24 +1285,24 @@
         <v>46278.581944444501</v>
       </c>
       <c r="G25" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="16.5">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C26" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1492,24 +1314,24 @@
         <v>46279.673611111102</v>
       </c>
       <c r="G26" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="16.5">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C27" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1521,24 +1343,24 @@
         <v>46280.456944444501</v>
       </c>
       <c r="G27" t="s">
+        <v>29</v>
+      </c>
+      <c r="H27" t="s">
         <v>30</v>
       </c>
-      <c r="H27" t="s">
-        <v>31</v>
-      </c>
       <c r="I27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="16.5">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C28" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1550,24 +1372,24 @@
         <v>46280.8881944444</v>
       </c>
       <c r="G28" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="16.5">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C29" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1579,24 +1401,24 @@
         <v>46281.684722222199</v>
       </c>
       <c r="G29" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="16.5">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C30" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1608,24 +1430,24 @@
         <v>46282.504166666702</v>
       </c>
       <c r="G30" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="16.5">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C31" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1637,24 +1459,24 @@
         <v>46282.8930555556</v>
       </c>
       <c r="G31" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="16.5">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C32" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1666,53 +1488,53 @@
         <v>46283.684027777803</v>
       </c>
       <c r="G32" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="16.5">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C33" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D33">
         <v>32</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F33" s="6">
         <v>46285.502777777801</v>
       </c>
       <c r="G33" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I33" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="16.5">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C34" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1724,24 +1546,24 @@
         <v>46285.939583333296</v>
       </c>
       <c r="G34" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I34" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="16.5">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C35" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1753,24 +1575,24 @@
         <v>46286.840277777803</v>
       </c>
       <c r="G35" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H35" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I35" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="16.5">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C36" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1782,24 +1604,24 @@
         <v>46287.545138888898</v>
       </c>
       <c r="G36" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I36" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="16.5">
       <c r="A37" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C37" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1811,24 +1633,24 @@
         <v>46288.458333333299</v>
       </c>
       <c r="G37" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I37" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="16.5">
       <c r="A38" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B38" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C38" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1840,24 +1662,24 @@
         <v>46288.847222222197</v>
       </c>
       <c r="G38" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H38" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I38" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="16.5">
       <c r="A39" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C39" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1869,24 +1691,24 @@
         <v>46291.416666666701</v>
       </c>
       <c r="G39" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I39" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="16.5">
       <c r="A40" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B40" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C40" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1898,24 +1720,24 @@
         <v>46292.397916666698</v>
       </c>
       <c r="G40" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H40" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I40" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="16.5">
       <c r="A41" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C41" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1927,24 +1749,24 @@
         <v>46293.438194444403</v>
       </c>
       <c r="G41" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I41" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="16.5">
       <c r="A42" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C42" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1956,24 +1778,24 @@
         <v>46294.520833333299</v>
       </c>
       <c r="G42" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H42" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I42" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="16.5">
       <c r="A43" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B43" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C43" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1985,24 +1807,24 @@
         <v>46300.426388888904</v>
       </c>
       <c r="G43" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H43" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I43" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="16.5">
       <c r="A44" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B44" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C44" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -2014,24 +1836,24 @@
         <v>46303.502777777801</v>
       </c>
       <c r="G44" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H44" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I44" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="16.5">
       <c r="A45" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B45" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C45" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -2043,24 +1865,24 @@
         <v>46303.958333333299</v>
       </c>
       <c r="G45" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H45" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I45" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="16.5">
       <c r="A46" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B46" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C46" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -2072,24 +1894,24 @@
         <v>46304.770833333299</v>
       </c>
       <c r="G46" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I46" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="16.5">
       <c r="A47" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B47" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C47" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -2101,24 +1923,24 @@
         <v>46307.583333333299</v>
       </c>
       <c r="G47" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H47" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I47" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="16.5">
       <c r="A48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B48" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C48" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -2130,24 +1952,24 @@
         <v>46308.604166666701</v>
       </c>
       <c r="G48" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H48" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I48" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="16.5">
       <c r="A49" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B49" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C49" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -2159,24 +1981,24 @@
         <v>46309.5</v>
       </c>
       <c r="G49" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H49" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I49" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="16.5">
       <c r="A50" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B50" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C50" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -2188,24 +2010,24 @@
         <v>46309.968055555597</v>
       </c>
       <c r="G50" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H50" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I50" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="16.5">
       <c r="A51" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B51" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C51" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -2217,24 +2039,24 @@
         <v>46310.762499999997</v>
       </c>
       <c r="G51" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H51" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I51" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="16.5">
       <c r="A52" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B52" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C52" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -2246,24 +2068,24 @@
         <v>46313.715277777803</v>
       </c>
       <c r="G52" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H52" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I52" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="16.5">
       <c r="A53" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B53" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C53" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -2275,24 +2097,24 @@
         <v>46314.645833333299</v>
       </c>
       <c r="G53" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H53" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I53" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="16.5">
       <c r="A54" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B54" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C54" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -2304,24 +2126,24 @@
         <v>46315.4375</v>
       </c>
       <c r="G54" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H54" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I54" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="16.5">
       <c r="A55" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B55" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C55" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -2333,24 +2155,24 @@
         <v>46315.791666666701</v>
       </c>
       <c r="G55" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H55" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I55" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="16.5">
       <c r="A56" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B56" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C56" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -2362,24 +2184,24 @@
         <v>46316.4375</v>
       </c>
       <c r="G56" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H56" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I56" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="16.5">
       <c r="A57" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B57" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C57" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -2391,24 +2213,24 @@
         <v>46316.734722222202</v>
       </c>
       <c r="G57" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H57" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I57" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="16.5">
       <c r="A58" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B58" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C58" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -2420,24 +2242,24 @@
         <v>46317.4375</v>
       </c>
       <c r="G58" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H58" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I58" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="16.5">
       <c r="A59" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B59" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C59" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -2446,27 +2268,27 @@
         <v>46317.4375</v>
       </c>
       <c r="F59" t="s">
-        <v>104</v>
+        <v>50</v>
       </c>
       <c r="G59" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H59" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I59" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="16.5">
       <c r="A60" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B60" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C60" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -2478,24 +2300,24 @@
         <v>46321.846527777801</v>
       </c>
       <c r="G60" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H60" t="s">
-        <v>105</v>
+        <v>51</v>
       </c>
       <c r="I60" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="16.5">
       <c r="A61" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B61" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C61" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2504,13 +2326,13 @@
         <v>46321.846527777801</v>
       </c>
       <c r="G61" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H61" t="s">
-        <v>106</v>
+        <v>52</v>
       </c>
       <c r="I61" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2518,473 +2340,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <sheetPr codeName="刀具调查"/>
-  <dimension ref="A1:R9"/>
-  <sheetFormatPr defaultColWidth="14.21875" defaultRowHeight="18" customHeight="1"/>
-  <cols>
-    <col min="1" max="5" width="9.6640625" customWidth="1"/>
-    <col min="6" max="6" width="19.6640625" customWidth="1"/>
-    <col min="7" max="9" width="9.6640625" customWidth="1"/>
-    <col min="10" max="10" width="32" customWidth="1"/>
-    <col min="11" max="14" width="9.6640625" customWidth="1"/>
-    <col min="15" max="15" width="34.5546875" customWidth="1"/>
-    <col min="16" max="18" width="9.6640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:18" ht="18" customHeight="1">
-      <c r="A1" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="J1" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="K1" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="L1" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="M1" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="N1" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="O1" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="P1" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q1" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="R1" s="10" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" ht="18" customHeight="1">
-      <c r="A2" s="12">
-        <v>4152</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="E2" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="F2" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="G2" s="13">
-        <v>110</v>
-      </c>
-      <c r="H2" s="13">
-        <v>200</v>
-      </c>
-      <c r="I2" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="J2" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="K2" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="L2" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="M2" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="N2" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="O2" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="P2" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q2" s="13"/>
-      <c r="R2" s="13"/>
-    </row>
-    <row r="3" spans="1:18" ht="18" customHeight="1">
-      <c r="A3" s="12">
-        <v>4152</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="G3" s="13">
-        <v>110</v>
-      </c>
-      <c r="H3" s="13">
-        <v>200</v>
-      </c>
-      <c r="I3" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="J3" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="K3" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="L3" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="M3" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="N3" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="O3" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="P3" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="13"/>
-    </row>
-    <row r="4" spans="1:18" ht="18" customHeight="1">
-      <c r="A4" s="12">
-        <v>4111</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="G4" s="12">
-        <v>150</v>
-      </c>
-      <c r="H4" s="12">
-        <v>1500</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="J4" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="K4" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="L4" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="M4" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="N4" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="O4" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="P4" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q4" s="12"/>
-      <c r="R4" s="12"/>
-    </row>
-    <row r="5" spans="1:18" ht="18" customHeight="1">
-      <c r="A5" s="12">
-        <v>4111</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="G5" s="12">
-        <v>150</v>
-      </c>
-      <c r="H5" s="12">
-        <v>1500</v>
-      </c>
-      <c r="I5" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="J5" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="K5" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="L5" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="M5" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="N5" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="O5" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="P5" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q5" s="12"/>
-      <c r="R5" s="12"/>
-    </row>
-    <row r="6" spans="1:18" ht="18" customHeight="1">
-      <c r="A6" s="12">
-        <v>2094</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="G6" s="12">
-        <v>8</v>
-      </c>
-      <c r="H6" s="12">
-        <v>50</v>
-      </c>
-      <c r="I6" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="J6" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="K6" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="L6" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="M6" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="N6" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="O6" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="P6" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q6" s="12"/>
-      <c r="R6" s="12"/>
-    </row>
-    <row r="7" spans="1:18" ht="18" customHeight="1">
-      <c r="A7">
-        <v>2575</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" t="s">
-        <v>91</v>
-      </c>
-      <c r="D7" t="s">
-        <v>92</v>
-      </c>
-      <c r="E7" t="s">
-        <v>93</v>
-      </c>
-      <c r="F7" t="s">
-        <v>94</v>
-      </c>
-      <c r="G7">
-        <v>270</v>
-      </c>
-      <c r="H7">
-        <v>600</v>
-      </c>
-      <c r="I7" t="s">
-        <v>95</v>
-      </c>
-      <c r="J7" t="s">
-        <v>96</v>
-      </c>
-      <c r="M7" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="N7" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="O7" t="s">
-        <v>97</v>
-      </c>
-      <c r="P7" s="13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" ht="18" customHeight="1">
-      <c r="A8">
-        <v>2575</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" t="s">
-        <v>98</v>
-      </c>
-      <c r="D8" t="s">
-        <v>99</v>
-      </c>
-      <c r="E8" t="s">
-        <v>93</v>
-      </c>
-      <c r="F8" t="s">
-        <v>100</v>
-      </c>
-      <c r="G8">
-        <v>270</v>
-      </c>
-      <c r="H8">
-        <v>600</v>
-      </c>
-      <c r="I8" t="s">
-        <v>95</v>
-      </c>
-      <c r="J8" t="s">
-        <v>96</v>
-      </c>
-      <c r="M8" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="N8" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="O8" t="s">
-        <v>97</v>
-      </c>
-      <c r="P8" s="13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" ht="18" customHeight="1">
-      <c r="A9">
-        <v>2575</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" t="s">
-        <v>101</v>
-      </c>
-      <c r="D9" t="s">
-        <v>102</v>
-      </c>
-      <c r="E9" t="s">
-        <v>93</v>
-      </c>
-      <c r="F9" t="s">
-        <v>103</v>
-      </c>
-      <c r="G9">
-        <v>270</v>
-      </c>
-      <c r="H9">
-        <v>600</v>
-      </c>
-      <c r="I9" t="s">
-        <v>95</v>
-      </c>
-      <c r="J9" t="s">
-        <v>96</v>
-      </c>
-      <c r="M9" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="N9" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="O9" t="s">
-        <v>97</v>
-      </c>
-      <c r="P9" s="13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>